--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY140"/>
+  <dimension ref="A1:AZ140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129446794</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129488204</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133345608</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129443295</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129470877</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1388,6 +1418,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129471390</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1495,6 +1530,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129538366</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1619,6 +1659,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129538535</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1726,6 +1771,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607514</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1850,6 +1900,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669409</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1966,6 +2021,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669654</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2082,6 +2142,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669660</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2216,6 +2281,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129488038</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2335,6 +2405,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129492825</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2459,6 +2534,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129533705</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2583,6 +2663,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129541326</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2699,6 +2784,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129602326</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2818,6 +2908,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129444530</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2937,6 +3032,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129444678</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3057,6 +3157,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129446217</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3186,6 +3291,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129489293</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3310,6 +3420,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129542151</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3434,6 +3549,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129542189</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3553,6 +3673,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129493076</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3677,6 +3802,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129494887</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3796,6 +3926,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129541381</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3915,6 +4050,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129469261</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4035,6 +4175,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129470787</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4154,6 +4299,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472815</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4273,6 +4423,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607027</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4392,6 +4547,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607102</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4508,6 +4668,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669008</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4627,6 +4792,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669051</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4751,6 +4921,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669277</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4870,6 +5045,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129467770</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4989,6 +5169,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129484713</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5100,6 +5285,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129485199</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5207,6 +5397,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120248947</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5331,6 +5526,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129541948</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5450,6 +5650,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129542223</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5569,6 +5774,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607142</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5685,6 +5895,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129601136</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5800,6 +6015,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129482750</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5915,6 +6135,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129483542</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6039,6 +6264,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129487321</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6159,6 +6389,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491545</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6274,6 +6509,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129538574</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6394,6 +6634,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129540271</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6509,6 +6754,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668255</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6620,6 +6870,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669032</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6736,6 +6991,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129443610</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6847,6 +7107,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129600740</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6972,6 +7237,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491429</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7092,6 +7362,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129492183</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7212,6 +7487,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129492468</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7332,6 +7612,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129540175</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7452,6 +7737,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129568943</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7574,6 +7864,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104217277</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7681,6 +7976,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129445784</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7799,6 +8099,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129486936</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7906,6 +8211,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129491832</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8013,6 +8323,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129539323</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8128,6 +8443,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129482965</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8243,6 +8563,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129492601</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8355,6 +8680,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129442092</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8470,6 +8800,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462587</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8585,6 +8920,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129482928</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8700,6 +9040,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129487364</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8816,6 +9161,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129533550</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8923,6 +9273,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129601471</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9035,6 +9390,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129442624</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9152,6 +9512,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129468353</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9265,6 +9630,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129482998</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9383,6 +9753,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129483526</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9506,6 +9881,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490326</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9629,6 +10009,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490370</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9736,6 +10121,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129493485</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9843,6 +10233,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495523</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9961,6 +10356,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133345742</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10082,6 +10482,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104217709</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10202,6 +10607,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464509</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10327,6 +10737,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464731</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10447,6 +10862,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464900</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10567,6 +10987,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465000</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10687,6 +11112,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465138</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10807,6 +11237,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465776</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10927,6 +11362,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466275</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11047,6 +11487,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466413</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11167,6 +11612,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466484</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11287,6 +11737,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466579</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11407,6 +11862,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466678</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11527,6 +11987,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466851</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11647,6 +12112,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466898</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11767,6 +12237,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129466948</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11878,6 +12353,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129467138</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11998,6 +12478,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129467585</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12118,6 +12603,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129471145</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12238,6 +12728,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472963</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12358,6 +12853,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129483716</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12478,6 +12978,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129483958</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12594,6 +13099,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129606047</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12710,6 +13220,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129606368</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12826,6 +13341,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129606685</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12942,6 +13462,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607002</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13058,6 +13583,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607050</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13174,6 +13704,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607114</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13290,6 +13825,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607141</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13406,6 +13946,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607156</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13522,6 +14067,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607239</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13638,6 +14188,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607279</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13754,6 +14309,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607341</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13870,6 +14430,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607516</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13995,6 +14560,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129667937</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14111,6 +14681,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668007</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14227,6 +14802,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668091</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14343,6 +14923,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668098</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14459,6 +15044,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668148</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14579,6 +15169,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668272</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14699,6 +15294,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668456</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14819,6 +15419,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668501</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14944,6 +15549,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668536</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15064,6 +15674,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668673</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15189,6 +15804,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668933</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15314,6 +15934,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669000</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15434,6 +16059,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669118</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15554,6 +16184,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669192</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15679,6 +16314,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669211</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15804,6 +16444,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669294</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15929,6 +16574,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669313</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -16054,6 +16704,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669333</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -16189,6 +16844,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669372</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16296,6 +16956,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129440979</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16403,6 +17068,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129443245</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16510,6 +17180,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129482646</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16635,6 +17310,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129483410</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16742,6 +17422,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129538294</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16859,6 +17544,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129538564</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16976,6 +17666,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129540902</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -17096,8 +17791,154 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129668693</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93215</v>
+        <v>93365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93381</v>
+        <v>93382</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93382</v>
+        <v>93383</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93383</v>
+        <v>93389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93396</v>
+        <v>93403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93404</v>
+        <v>93417</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
